--- a/artfynd/A 63543-2025 artfynd.xlsx
+++ b/artfynd/A 63543-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>105375365</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>689205.1437435169</v>
+        <v>689205</v>
       </c>
       <c r="R2" t="n">
-        <v>6608778.692731675</v>
+        <v>6608778</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -789,6 +784,220 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126358115</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Roslagsleden, Roslagsleden, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>689303</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6608672</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126358032</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Roslagsleden, Roslagsleden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>689304</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6608667</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Össeby-Garn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
